--- a/SIGO-G-012_Riesgos_Fatalidad_CCP_CCM.xlsx
+++ b/SIGO-G-012_Riesgos_Fatalidad_CCP_CCM.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
     <font>
@@ -61,7 +66,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -75,11 +80,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -101,37 +121,200 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,14 +680,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:F164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,10 +698,10 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Columnas "Implementación" y "Valorización CLP" quedan a completar por el equipo de Prevención de Riesgos / SSO según la realidad de cada faena o contrato.</t>
+          <t>Cada Control Crítico (CCP = Preventivo, CCM = Mitigador) se presenta en su propio recuadro. Las columnas "Implementación" y "Valorización CLP" quedan a completar por el equipo de Prevención de Riesgos / SSO según la realidad de cada faena o contrato.</t>
         </is>
       </c>
     </row>
@@ -534,22 +718,26 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Controles Críticos (Preventivos/Mitigadores).
-CCP - CCM</t>
+          <t>Código</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>Control Crítico (CCP - Preventivo / CCM - Mitigador)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Valorización CLP</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="108.5" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
@@ -560,661 +748,2783 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>CCP1 - Personal Acreditado para trabajos eléctricos
-CCP2 - Acceso restringido a equipos e instalaciones eléctricas
-CCP3 - Equipos y Herramientas eléctricas verificadas
-CCP4 - Intervención de Equipos en Condición Eléctricamente Segura
-CCM1 - Selección y uso de EPP específico para la actividad
-CCM2 - Protecciones eléctricas en sistemas de alta y media tensión
-CCM3 - Capacidad de Respuesta Ante Emergencia</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="n"/>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Personal Acreditado para trabajos eléctricos</t>
+        </is>
+      </c>
       <c r="E5" s="8" t="n"/>
-    </row>
-    <row r="6" ht="77.5" customHeight="1">
-      <c r="A6" s="4" t="n">
+      <c r="F5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Acceso restringido a equipos e instalaciones eléctricas</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="15" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Equipos y Herramientas eléctricas verificadas</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="15" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>CCP4</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Intervención de Equipos en Condición Eléctricamente Segura</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="15" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Selección y uso de EPP específico para la actividad</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="15" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Protecciones eléctricas en sistemas de alta y media tensión</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="18" t="n"/>
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>CCM3</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de Respuesta Ante Emergencia</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>RF 02: Trabajo en Altura</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Plataformas y superficies de trabajo estables e íntegras
-CCP2 - Personal acreditado realiza trabajos en altura
-CCM1 - Uso Correcto de SPDC
-CCM2 - Conexión a Punto Anclaje Certificado
-CCM3 - Capacidad de Rescate en Suspensión</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="108.5" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Plataformas y superficies de trabajo estables e íntegras</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Personal acreditado realiza trabajos en altura</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="15" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Uso Correcto de SPDC</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>Conexión a Punto Anclaje Certificado</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="15" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="18" t="n"/>
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>CCM3</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de Rescate en Suspensión</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="23" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>RF 03: Maniobras de Izaje</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Equipos y elementos de izaje conforme a especificaciones técnicas
-CCP2 - Estabilizadores operativos y posicionamiento seguro de equipos de izaje móviles
-CCP3 - Personal acreditado para maniobras de izaje
-CCP4 - Comunicación bidireccional efectiva entre operador y rigger
-CCP5 - Plan de Izaje
-CCM1 - Segregación y control de acceso en área de maniobras
-CCM2 - Capacidad de respuesta ante emergencia</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="77.5" customHeight="1">
-      <c r="A8" s="4" t="n">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Equipos y elementos de izaje conforme a especificaciones técnicas</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Estabilizadores operativos y posicionamiento seguro de equipos de izaje móviles</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Personal acreditado para maniobras de izaje</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="15" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>CCP4</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Comunicación bidireccional efectiva entre operador y rigger</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>CCP5</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Plan de Izaje</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Segregación y control de acceso en área de maniobras</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="18" t="n"/>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta ante emergencia</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="23" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>RF 04: Liberación Descontrolada de Energías</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Identificación, aislación, bloqueo y verificación de energía cero
-CCP2 - Sistemas y elementos de contención de energía
-CCP3 - Dispositivos de protección y alivio de presión
-CCM1 - Segregación y Control de Acceso
-CCM2 - Capacidad de Respuesta Ante Emergencia</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="77.5" customHeight="1">
-      <c r="A9" s="4" t="n">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Identificación, aislación, bloqueo y verificación de energía cero</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Sistemas y elementos de contención de energía</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Dispositivos de protección y alivio de presión</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Segregación y Control de Acceso</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="15" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="18" t="n"/>
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de Respuesta Ante Emergencia</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="23" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>RF 05: Caída de Rocas en Mina Rajo</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Modelo y monitoreo geotécnico de estabilidad de taludes y bancos
-CCP2 - Saneamiento y limpieza de bermas y taludes
-CCP3 - Control topográfico y drenaje
-CCM1 - Segregación física y contención estructural
-CCM2 - Capacidad de Respuesta ante Emergencia</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="8" t="n"/>
-    </row>
-    <row r="10" ht="77.5" customHeight="1">
-      <c r="A10" s="4" t="n">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Modelo y monitoreo geotécnico de estabilidad de taludes y bancos</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Saneamiento y limpieza de bermas y taludes</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="15" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Control topográfico y drenaje</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Segregación física y contención estructural</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="18" t="n"/>
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de Respuesta ante Emergencia</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="23" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>RF 06: Incendio</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Mapeo de áreas críticas y Gestión de Materiales Combustibles e Inflamables
-CCP2 - Control de trabajos en caliente
-CCP3 - Sistemas de protección contra fuentes de ignición
-CCM1 - Sistemas de detección y extinción de incendios
-CCM2 - Capacidad de Respuesta ante emergencias</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="8" t="n"/>
-    </row>
-    <row r="11" ht="77.5" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Mapeo de áreas críticas y Gestión de Materiales Combustibles e Inflamables</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="9" t="n"/>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Control de trabajos en caliente</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="15" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Sistemas de protección contra fuentes de ignición</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="15" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>Sistemas de detección y extinción de incendios</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="15" t="n"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="18" t="n"/>
+      <c r="B38" s="19" t="n"/>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de Respuesta ante emergencias</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="23" t="n"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>RF 07: Sustancias Peligrosas</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Diseño, operación y señalización en procesos de manejo y almacenamiento de sustancias químicas peligrosas
-CCP2 - Competencias de acuerdo a roles y funciones para manipulación segura de sustancias químicas peligrosas
-CCP3 - Aislación, bloqueo y segregación para sustancias peligrosas
-CCM1 - Sistemas de detección/control de fugas, derrames, incendios y EPP químicos
-CCM2 - Capacidad de respuesta ante emergencia química</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="8" t="n"/>
-    </row>
-    <row r="12" ht="93" customHeight="1">
-      <c r="A12" s="4" t="n">
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Diseño, operación y señalización en procesos de manejo y almacenamiento de sustancias químicas peligrosas</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Competencias de acuerdo a roles y funciones para manipulación segura de sustancias químicas peligrosas</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="15" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>Aislación, bloqueo y segregación para sustancias peligrosas</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="15" t="n"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>Sistemas de detección/control de fugas, derrames, incendios y EPP químicos</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="15" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="18" t="n"/>
+      <c r="B43" s="19" t="n"/>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta ante emergencia química</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="23" t="n"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>RF 08: Tronaduras y Explosivos</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Personal acreditado en tronadura y manejo de explosivos
-CCP2 - Tronaduras ejecutadas según diseño aprobado
-CCP3 - Diseño y ejecución de tronadura conforme a condiciones reales
-CCP4 - Aislación física y evacuación segura de la zona de tronadura
-CCP5 - Vehículos acreditados y seguros para transporte y fabricación de explosivos
-CCM1 - Capacidad de respuesta ante emergencia</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="8" t="n"/>
-    </row>
-    <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="4" t="n">
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Personal acreditado en tronadura y manejo de explosivos</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="9" t="n"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>Tronaduras ejecutadas según diseño aprobado</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="15" t="n"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="10" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>Diseño y ejecución de tronadura conforme a condiciones reales</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="n"/>
+      <c r="F46" s="15" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="10" t="n"/>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>CCP4</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>Aislación física y evacuación segura de la zona de tronadura</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="n"/>
+      <c r="F47" s="15" t="n"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="10" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>CCP5</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Vehículos acreditados y seguros para transporte y fabricación de explosivos</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="15" t="n"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="18" t="n"/>
+      <c r="B49" s="19" t="n"/>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta ante emergencia</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="n"/>
+      <c r="F49" s="23" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>RF 09: Partes Móviles</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Guardas y protecciones en partes móviles
-CCP2 - Aislación, bloqueo y verificación de energía cero
-CCM1 - Sistema de parada de emergencia
-CCM2 - Capacidad de respuesta ante emergencia</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="8" t="n"/>
-    </row>
-    <row r="14" ht="77.5" customHeight="1">
-      <c r="A14" s="4" t="n">
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Guardas y protecciones en partes móviles</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="9" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>Aislación, bloqueo y verificación de energía cero</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="n"/>
+      <c r="F51" s="15" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="10" t="n"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>Sistema de parada de emergencia</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="n"/>
+      <c r="F52" s="15" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="18" t="n"/>
+      <c r="B53" s="19" t="n"/>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta ante emergencia</t>
+        </is>
+      </c>
+      <c r="E53" s="22" t="n"/>
+      <c r="F53" s="23" t="n"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>RF 10: Vehículos</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Conductor acreditado y apto física y psicológicamente
-CCP2 - Integridad mecánica y sistemas activos del vehículo
-CCP3 - Sistema integral de asistencia y monitoreo a la conducción
-CCP4 - Infraestructura vial conforme a diseño
-CCM1 - Capacidad de respuesta ante emergencia</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="8" t="n"/>
-    </row>
-    <row r="15" ht="62" customHeight="1">
-      <c r="A15" s="4" t="n">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Conductor acreditado y apto física y psicológicamente</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="9" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="10" t="n"/>
+      <c r="B55" s="11" t="n"/>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>Integridad mecánica y sistemas activos del vehículo</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="n"/>
+      <c r="F55" s="15" t="n"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="10" t="n"/>
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>Sistema integral de asistencia y monitoreo a la conducción</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="n"/>
+      <c r="F56" s="15" t="n"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="10" t="n"/>
+      <c r="B57" s="11" t="n"/>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>CCP4</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>Infraestructura vial conforme a diseño</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="n"/>
+      <c r="F57" s="15" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="18" t="n"/>
+      <c r="B58" s="19" t="n"/>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D58" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta ante emergencia</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="n"/>
+      <c r="F58" s="23" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>RF 11: Espacios Confinados</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Sistema de ingreso controlado y vigilado
-CCP2 - Evaluación y monitoreo de atmósfera
-CCP3 - Identificación y preparación de espacios confinados
-CCM1 - Capacidad de respuesta y rescate ante emergencia en espacios confinados</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="8" t="n"/>
-    </row>
-    <row r="16" ht="93" customHeight="1">
-      <c r="A16" s="4" t="n">
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Sistema de ingreso controlado y vigilado</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="9" t="n"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="10" t="n"/>
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>Evaluación y monitoreo de atmósfera</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="n"/>
+      <c r="F60" s="15" t="n"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="10" t="n"/>
+      <c r="B61" s="11" t="n"/>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>Identificación y preparación de espacios confinados</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="n"/>
+      <c r="F61" s="15" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="18" t="n"/>
+      <c r="B62" s="19" t="n"/>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D62" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta y rescate ante emergencia en espacios confinados</t>
+        </is>
+      </c>
+      <c r="E62" s="22" t="n"/>
+      <c r="F62" s="23" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>RF 12: Metales Fundidos</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Personal capacitado para trabajar con metales fundidos
-CCP2 - Control de acceso a áreas de fundición
-CCP3 - Control operacional del metal fundido (traslado, monitoreo, refrigeración)
-CCP4 - Control de humedad en operaciones con metal fundido
-CCM1 - Protección personal y estructural contra metal fundido (EPP, casetas y contención)
-CCM2 - Capacidad de respuesta y Rescate ante emergencia</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="8" t="n"/>
-    </row>
-    <row r="17" ht="62" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Personal capacitado para trabajar con metales fundidos</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="n"/>
+      <c r="F63" s="9" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="10" t="n"/>
+      <c r="B64" s="11" t="n"/>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>Control de acceso a áreas de fundición</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="n"/>
+      <c r="F64" s="15" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="10" t="n"/>
+      <c r="B65" s="11" t="n"/>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>Control operacional del metal fundido (traslado, monitoreo, refrigeración)</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="n"/>
+      <c r="F65" s="15" t="n"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="10" t="n"/>
+      <c r="B66" s="11" t="n"/>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>CCP4</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>Control de humedad en operaciones con metal fundido</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="n"/>
+      <c r="F66" s="15" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="10" t="n"/>
+      <c r="B67" s="11" t="n"/>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>Protección personal y estructural contra metal fundido (EPP, casetas y contención)</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="n"/>
+      <c r="F67" s="15" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="18" t="n"/>
+      <c r="B68" s="19" t="n"/>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D68" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta y Rescate ante emergencia</t>
+        </is>
+      </c>
+      <c r="E68" s="22" t="n"/>
+      <c r="F68" s="23" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>RF 13: Caída de Objetos</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Estructuras y materiales sujetos en altura
-CCP2 - Control de trabajos en la vertical
-CCM1 - Sistemas de contención y segregación
-CCM2 - Capacidad de respuesta ante emergencia</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="8" t="n"/>
-    </row>
-    <row r="18" ht="62" customHeight="1">
-      <c r="A18" s="4" t="n">
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Estructuras y materiales sujetos en altura</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="9" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="10" t="n"/>
+      <c r="B70" s="11" t="n"/>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>Control de trabajos en la vertical</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="n"/>
+      <c r="F70" s="15" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="10" t="n"/>
+      <c r="B71" s="11" t="n"/>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="inlineStr">
+        <is>
+          <t>Sistemas de contención y segregación</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="n"/>
+      <c r="F71" s="15" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="18" t="n"/>
+      <c r="B72" s="19" t="n"/>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D72" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta ante emergencia</t>
+        </is>
+      </c>
+      <c r="E72" s="22" t="n"/>
+      <c r="F72" s="23" t="n"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>RF 14: Operación Ferroviaria</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Personal ferroviario acreditado y autorizado
-CCP2 - Integridad operativa de vías y equipos ferroviarios
-CCP3 - Gestión Integral del Tráfico Ferroviario y Protección de Cuadrillas
-CCM1 - Capacidad de respuesta ante emergencias ferroviarias</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="8" t="n"/>
-    </row>
-    <row r="19" ht="108.5" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Personal ferroviario acreditado y autorizado</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="n"/>
+      <c r="F73" s="9" t="n"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="10" t="n"/>
+      <c r="B74" s="11" t="n"/>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>Integridad operativa de vías y equipos ferroviarios</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="n"/>
+      <c r="F74" s="15" t="n"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="10" t="n"/>
+      <c r="B75" s="11" t="n"/>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>Gestión Integral del Tráfico Ferroviario y Protección de Cuadrillas</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="n"/>
+      <c r="F75" s="15" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="18" t="n"/>
+      <c r="B76" s="19" t="n"/>
+      <c r="C76" s="20" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D76" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta ante emergencias ferroviarias</t>
+        </is>
+      </c>
+      <c r="E76" s="22" t="n"/>
+      <c r="F76" s="23" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>RF 15: Avalancha y Aludes</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Zonificación de peligro de avalanchas aplicada a toda instalación en superficie
-CCP2 - Sistema de alertas tempranas y estructura organizacional de invierno operativa
-CCP3 - Monitoreo nivo-meteorológico con instrumental operativo y emisión de Boletín de riesgos (BDR)
-CCP4 - Ejecución del desencadenamiento preventivo con áreas evacuadas y segregadas
-CCP5 - Sistemas Remotos de Control de Avalanchas (RACS)
-CCM1 - Respuesta a emergencia y búsqueda y rescate de víctimas de avalancha
-CCM2 - Instalaciones con resistencia estructural en zona de peligro de avalancha</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="8" t="n"/>
-    </row>
-    <row r="20" ht="62" customHeight="1">
-      <c r="A20" s="4" t="n">
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Zonificación de peligro de avalanchas aplicada a toda instalación en superficie</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="9" t="n"/>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="10" t="n"/>
+      <c r="B78" s="11" t="n"/>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>Sistema de alertas tempranas y estructura organizacional de invierno operativa</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="n"/>
+      <c r="F78" s="15" t="n"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="10" t="n"/>
+      <c r="B79" s="11" t="n"/>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>Monitoreo nivo-meteorológico con instrumental operativo y emisión de Boletín de riesgos (BDR)</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="n"/>
+      <c r="F79" s="15" t="n"/>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="10" t="n"/>
+      <c r="B80" s="11" t="n"/>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>CCP4</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>Ejecución del desencadenamiento preventivo con áreas evacuadas y segregadas</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="n"/>
+      <c r="F80" s="15" t="n"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="10" t="n"/>
+      <c r="B81" s="11" t="n"/>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>CCP5</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>Sistemas Remotos de Control de Avalanchas (RACS)</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="n"/>
+      <c r="F81" s="15" t="n"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="10" t="n"/>
+      <c r="B82" s="11" t="n"/>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>Respuesta a emergencia y búsqueda y rescate de víctimas de avalancha</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="n"/>
+      <c r="F82" s="15" t="n"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="18" t="n"/>
+      <c r="B83" s="19" t="n"/>
+      <c r="C83" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>Instalaciones con resistencia estructural en zona de peligro de avalancha</t>
+        </is>
+      </c>
+      <c r="E83" s="22" t="n"/>
+      <c r="F83" s="23" t="n"/>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>RF 16: Vaciados, Chimeneas y Piques</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Condiciones seguras de ingreso y operación en piques y chimeneas
-CCP2 - Fortificación y sellado de excavaciones verticales
-CCM1 - Sistemas de protección contra caídas
-CCM2 - Capacidad de respuesta y rescate ante emergencia</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="8" t="n"/>
-    </row>
-    <row r="21" ht="62" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Condiciones seguras de ingreso y operación en piques y chimeneas</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="n"/>
+      <c r="F84" s="9" t="n"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="10" t="n"/>
+      <c r="B85" s="11" t="n"/>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>Fortificación y sellado de excavaciones verticales</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="n"/>
+      <c r="F85" s="15" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="10" t="n"/>
+      <c r="B86" s="11" t="n"/>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>Sistemas de protección contra caídas</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="n"/>
+      <c r="F86" s="15" t="n"/>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="18" t="n"/>
+      <c r="B87" s="19" t="n"/>
+      <c r="C87" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta y rescate ante emergencia</t>
+        </is>
+      </c>
+      <c r="E87" s="22" t="n"/>
+      <c r="F87" s="23" t="n"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>RF 17: Bombeo de Agua Barro</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Caracterización y delimitación de áreas de extracción con riesgo de bombeo de agua-barro
-CCP2 - Extracción en zonas de barro mediante telecomando o sistemas autónomos
-CCP3 - Gestión de secuencia y tasa de extracción conforme a diseño aprobado
-CCP4 - Integridad estructural en puntos de extracción, piques, buzones y chimeneas</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="8" t="n"/>
-    </row>
-    <row r="22" ht="77.5" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Caracterización y delimitación de áreas de extracción con riesgo de bombeo de agua-barro</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="n"/>
+      <c r="F88" s="9" t="n"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="10" t="n"/>
+      <c r="B89" s="11" t="n"/>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>Extracción en zonas de barro mediante telecomando o sistemas autónomos</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="n"/>
+      <c r="F89" s="15" t="n"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="10" t="n"/>
+      <c r="B90" s="11" t="n"/>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>Gestión de secuencia y tasa de extracción conforme a diseño aprobado</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="n"/>
+      <c r="F90" s="15" t="n"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="18" t="n"/>
+      <c r="B91" s="19" t="n"/>
+      <c r="C91" s="24" t="inlineStr">
+        <is>
+          <t>CCP4</t>
+        </is>
+      </c>
+      <c r="D91" s="25" t="inlineStr">
+        <is>
+          <t>Integridad estructural en puntos de extracción, piques, buzones y chimeneas</t>
+        </is>
+      </c>
+      <c r="E91" s="22" t="n"/>
+      <c r="F91" s="23" t="n"/>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>RF 18: Planchoneo</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Estabilización conforme a diseño geotécnico (sostenimiento, fortificación y acuñadura)
-CCP2 - Perforación y tronadura conforme a diseño geotécnico
-CCM1 - Segregación y control de acceso
-CCM2 - Operación remota en zonas críticas
-CCM3 - Capacidad de Respuesta ante emergencias</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="8" t="n"/>
-    </row>
-    <row r="23" ht="93" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Estabilización conforme a diseño geotécnico (sostenimiento, fortificación y acuñadura)</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="n"/>
+      <c r="F92" s="9" t="n"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="10" t="n"/>
+      <c r="B93" s="11" t="n"/>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>Perforación y tronadura conforme a diseño geotécnico</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="n"/>
+      <c r="F93" s="15" t="n"/>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="10" t="n"/>
+      <c r="B94" s="11" t="n"/>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D94" s="17" t="inlineStr">
+        <is>
+          <t>Segregación y control de acceso</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="n"/>
+      <c r="F94" s="15" t="n"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="10" t="n"/>
+      <c r="B95" s="11" t="n"/>
+      <c r="C95" s="16" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D95" s="17" t="inlineStr">
+        <is>
+          <t>Operación remota en zonas críticas</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="n"/>
+      <c r="F95" s="15" t="n"/>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="18" t="n"/>
+      <c r="B96" s="19" t="n"/>
+      <c r="C96" s="20" t="inlineStr">
+        <is>
+          <t>CCM3</t>
+        </is>
+      </c>
+      <c r="D96" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de Respuesta ante emergencias</t>
+        </is>
+      </c>
+      <c r="E96" s="22" t="n"/>
+      <c r="F96" s="23" t="n"/>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>RF 19: Estallido de Rocas</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Diseño de excavaciones subterráneas
-CCP2 - Sistema de monitoreo geomecánico
-CCP3 - Control de procesos de PYT, desarrollo y pre acondicionamiento del macizo rocoso
-CCP4 - Soporte y Fortificación instalada conforme a diseño geomecánico
-CCM1 - Segregación y control de acceso autorizado en zona de transición (ZT)
-CCM2 - Capacidad de respuesta ante emergencias por Estallido de Rocas</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="8" t="n"/>
-    </row>
-    <row r="24" ht="77.5" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Diseño de excavaciones subterráneas</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="n"/>
+      <c r="F97" s="9" t="n"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="10" t="n"/>
+      <c r="B98" s="11" t="n"/>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="inlineStr">
+        <is>
+          <t>Sistema de monitoreo geomecánico</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="n"/>
+      <c r="F98" s="15" t="n"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="10" t="n"/>
+      <c r="B99" s="11" t="n"/>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>Control de procesos de PYT, desarrollo y pre acondicionamiento del macizo rocoso</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="n"/>
+      <c r="F99" s="15" t="n"/>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="10" t="n"/>
+      <c r="B100" s="11" t="n"/>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>CCP4</t>
+        </is>
+      </c>
+      <c r="D100" s="13" t="inlineStr">
+        <is>
+          <t>Soporte y Fortificación instalada conforme a diseño geomecánico</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="n"/>
+      <c r="F100" s="15" t="n"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="10" t="n"/>
+      <c r="B101" s="11" t="n"/>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D101" s="17" t="inlineStr">
+        <is>
+          <t>Segregación y control de acceso autorizado en zona de transición (ZT)</t>
+        </is>
+      </c>
+      <c r="E101" s="14" t="n"/>
+      <c r="F101" s="15" t="n"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="18" t="n"/>
+      <c r="B102" s="19" t="n"/>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D102" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta ante emergencias por Estallido de Rocas</t>
+        </is>
+      </c>
+      <c r="E102" s="22" t="n"/>
+      <c r="F102" s="23" t="n"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>RF 20: Sílice</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Supresión, humectación, colección y confinamiento de fuentes
-CCP2 - Control de emisiones en equipos productivos
-CCM1 - Ventilación subterránea y presurización de cabinas e instalaciones
-CCM2 - Aseo industrial no contaminante (control de dispersión)
-CCM3 - Protección respiratoria efectiva</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="8" t="n"/>
-    </row>
-    <row r="25" ht="77.5" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Supresión, humectación, colección y confinamiento de fuentes</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="n"/>
+      <c r="F103" s="9" t="n"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="10" t="n"/>
+      <c r="B104" s="11" t="n"/>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>Control de emisiones en equipos productivos</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="n"/>
+      <c r="F104" s="15" t="n"/>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="10" t="n"/>
+      <c r="B105" s="11" t="n"/>
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D105" s="17" t="inlineStr">
+        <is>
+          <t>Ventilación subterránea y presurización de cabinas e instalaciones</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="n"/>
+      <c r="F105" s="15" t="n"/>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="10" t="n"/>
+      <c r="B106" s="11" t="n"/>
+      <c r="C106" s="16" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="inlineStr">
+        <is>
+          <t>Aseo industrial no contaminante (control de dispersión)</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="n"/>
+      <c r="F106" s="15" t="n"/>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="18" t="n"/>
+      <c r="B107" s="19" t="n"/>
+      <c r="C107" s="20" t="inlineStr">
+        <is>
+          <t>CCM3</t>
+        </is>
+      </c>
+      <c r="D107" s="21" t="inlineStr">
+        <is>
+          <t>Protección respiratoria efectiva</t>
+        </is>
+      </c>
+      <c r="E107" s="22" t="n"/>
+      <c r="F107" s="23" t="n"/>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>RF 21: Arsénico</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Fuentes de arsénico identificadas, segregadas y restringidas
-CCP2 - Sistemas de captura y retención de arsénico operativos
-CCP3 - Aseo no contaminante de material arsenical (control de dispersión)
-CCM1 - Medidas higiénico sanitarias y Protección personal
-CCM2 - Monitoreo ocupacional de exposición y salud por arsénico</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="8" t="n"/>
-    </row>
-    <row r="26" ht="77.5" customHeight="1">
-      <c r="A26" s="4" t="n">
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Fuentes de arsénico identificadas, segregadas y restringidas</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="n"/>
+      <c r="F108" s="9" t="n"/>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="10" t="n"/>
+      <c r="B109" s="11" t="n"/>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D109" s="13" t="inlineStr">
+        <is>
+          <t>Sistemas de captura y retención de arsénico operativos</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="n"/>
+      <c r="F109" s="15" t="n"/>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="10" t="n"/>
+      <c r="B110" s="11" t="n"/>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D110" s="13" t="inlineStr">
+        <is>
+          <t>Aseo no contaminante de material arsenical (control de dispersión)</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="n"/>
+      <c r="F110" s="15" t="n"/>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="10" t="n"/>
+      <c r="B111" s="11" t="n"/>
+      <c r="C111" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="inlineStr">
+        <is>
+          <t>Medidas higiénico sanitarias y Protección personal</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="n"/>
+      <c r="F111" s="15" t="n"/>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="18" t="n"/>
+      <c r="B112" s="19" t="n"/>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D112" s="21" t="inlineStr">
+        <is>
+          <t>Monitoreo ocupacional de exposición y salud por arsénico</t>
+        </is>
+      </c>
+      <c r="E112" s="22" t="n"/>
+      <c r="F112" s="23" t="n"/>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B113" s="5" t="inlineStr">
         <is>
           <t>RF 22: Falla de Estructuras para Tránsito y Uso de Personas</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Diseño estructural y construcción de ETP conforme a normativa técnica vigente
-CCP2 - Inspección visual para identificar condiciones de riesgo a las personas en ETP
-CCP3 - Restitución de funcionalidad segura y conservación de las ETP operativas
-CCM1 - Segregación física y señalización de ETP con vanos abiertos o condiciones de riesgo
-CCM2 - Respuesta ante emergencia</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="8" t="n"/>
-    </row>
-    <row r="27" ht="93" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Diseño estructural y construcción de ETP conforme a normativa técnica vigente</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="n"/>
+      <c r="F113" s="9" t="n"/>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="10" t="n"/>
+      <c r="B114" s="11" t="n"/>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D114" s="13" t="inlineStr">
+        <is>
+          <t>Inspección visual para identificar condiciones de riesgo a las personas en ETP</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="n"/>
+      <c r="F114" s="15" t="n"/>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" s="10" t="n"/>
+      <c r="B115" s="11" t="n"/>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D115" s="13" t="inlineStr">
+        <is>
+          <t>Restitución de funcionalidad segura y conservación de las ETP operativas</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="n"/>
+      <c r="F115" s="15" t="n"/>
+    </row>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="10" t="n"/>
+      <c r="B116" s="11" t="n"/>
+      <c r="C116" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D116" s="17" t="inlineStr">
+        <is>
+          <t>Segregación física y señalización de ETP con vanos abiertos o condiciones de riesgo</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="n"/>
+      <c r="F116" s="15" t="n"/>
+    </row>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="18" t="n"/>
+      <c r="B117" s="19" t="n"/>
+      <c r="C117" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D117" s="21" t="inlineStr">
+        <is>
+          <t>Respuesta ante emergencia</t>
+        </is>
+      </c>
+      <c r="E117" s="22" t="n"/>
+      <c r="F117" s="23" t="n"/>
+    </row>
+    <row r="118" ht="30" customHeight="1">
+      <c r="A118" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>RF 23: Colapso Estructural del Macizo Rocoso</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Sistema de monitoreo geomecánico y control de la producción
-CCP2 - Estabilización conforme a diseño geotécnico (soporte y fortificación)
-CCP3 - Perforación y tronadura conforme a diseño geotécnico
-CCM1 - Segregación Física y Contención Estructural
-CCM2 - Operación remota de equipos en zonas críticas
-CCM3 - Capacidad de Respuesta Ante Emergencia</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="8" t="n"/>
-    </row>
-    <row r="28" ht="77.5" customHeight="1">
-      <c r="A28" s="4" t="n">
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>Sistema de monitoreo geomecánico y control de la producción</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="n"/>
+      <c r="F118" s="9" t="n"/>
+    </row>
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="10" t="n"/>
+      <c r="B119" s="11" t="n"/>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D119" s="13" t="inlineStr">
+        <is>
+          <t>Estabilización conforme a diseño geotécnico (soporte y fortificación)</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="n"/>
+      <c r="F119" s="15" t="n"/>
+    </row>
+    <row r="120" ht="30" customHeight="1">
+      <c r="A120" s="10" t="n"/>
+      <c r="B120" s="11" t="n"/>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D120" s="13" t="inlineStr">
+        <is>
+          <t>Perforación y tronadura conforme a diseño geotécnico</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="n"/>
+      <c r="F120" s="15" t="n"/>
+    </row>
+    <row r="121" ht="30" customHeight="1">
+      <c r="A121" s="10" t="n"/>
+      <c r="B121" s="11" t="n"/>
+      <c r="C121" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D121" s="17" t="inlineStr">
+        <is>
+          <t>Segregación Física y Contención Estructural</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="n"/>
+      <c r="F121" s="15" t="n"/>
+    </row>
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" s="10" t="n"/>
+      <c r="B122" s="11" t="n"/>
+      <c r="C122" s="16" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D122" s="17" t="inlineStr">
+        <is>
+          <t>Operación remota de equipos en zonas críticas</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="n"/>
+      <c r="F122" s="15" t="n"/>
+    </row>
+    <row r="123" ht="30" customHeight="1">
+      <c r="A123" s="18" t="n"/>
+      <c r="B123" s="19" t="n"/>
+      <c r="C123" s="20" t="inlineStr">
+        <is>
+          <t>CCM3</t>
+        </is>
+      </c>
+      <c r="D123" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de Respuesta Ante Emergencia</t>
+        </is>
+      </c>
+      <c r="E123" s="22" t="n"/>
+      <c r="F123" s="23" t="n"/>
+    </row>
+    <row r="124" ht="30" customHeight="1">
+      <c r="A124" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B124" s="5" t="inlineStr">
         <is>
           <t>RF 24: Taludes</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Sistema Integral de Caracterización y Modelamiento
-CCP2 - Perforación y tronadura conforme a diseño geotécnico (control de daño)
-CCP3 - Estabilización conforme a diseño geotécnico (saneamiento y fortificación de taludes)
-CCM1 - Pretiles y Segregación de Áreas
-CCM2 - Capacidad de Respuesta Ante Emergencia</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="8" t="n"/>
-    </row>
-    <row r="29" ht="93" customHeight="1">
-      <c r="A29" s="4" t="n">
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Sistema Integral de Caracterización y Modelamiento</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="n"/>
+      <c r="F124" s="9" t="n"/>
+    </row>
+    <row r="125" ht="30" customHeight="1">
+      <c r="A125" s="10" t="n"/>
+      <c r="B125" s="11" t="n"/>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>Perforación y tronadura conforme a diseño geotécnico (control de daño)</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="n"/>
+      <c r="F125" s="15" t="n"/>
+    </row>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="10" t="n"/>
+      <c r="B126" s="11" t="n"/>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D126" s="13" t="inlineStr">
+        <is>
+          <t>Estabilización conforme a diseño geotécnico (saneamiento y fortificación de taludes)</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="n"/>
+      <c r="F126" s="15" t="n"/>
+    </row>
+    <row r="127" ht="30" customHeight="1">
+      <c r="A127" s="10" t="n"/>
+      <c r="B127" s="11" t="n"/>
+      <c r="C127" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D127" s="17" t="inlineStr">
+        <is>
+          <t>Pretiles y Segregación de Áreas</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="n"/>
+      <c r="F127" s="15" t="n"/>
+    </row>
+    <row r="128" ht="30" customHeight="1">
+      <c r="A128" s="18" t="n"/>
+      <c r="B128" s="19" t="n"/>
+      <c r="C128" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D128" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de Respuesta Ante Emergencia</t>
+        </is>
+      </c>
+      <c r="E128" s="22" t="n"/>
+      <c r="F128" s="23" t="n"/>
+    </row>
+    <row r="129" ht="30" customHeight="1">
+      <c r="A129" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B129" s="5" t="inlineStr">
         <is>
           <t>RF 25: Equipos Mineros e Industriales</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Conductor acreditado y apto física y psicológicamente
-CCP2 - Sistema Integral de Asistencia y Monitoreo a la Conducción
-CCP3 - Integridad de componentes críticos del equipo (mecánicos, hidráulicos y eléctricos)
-CCP4 - Infraestructura vial conforme a diseño (bermas, pretiles, radios, drenaje)
-CCM1 - Cabinas de protección (ROPS y FOPS)
-CCM2 - Capacidad de respuesta ante emergencia</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="8" t="n"/>
-    </row>
-    <row r="30" ht="77.5" customHeight="1">
-      <c r="A30" s="4" t="n">
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Conductor acreditado y apto física y psicológicamente</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="n"/>
+      <c r="F129" s="9" t="n"/>
+    </row>
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="10" t="n"/>
+      <c r="B130" s="11" t="n"/>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D130" s="13" t="inlineStr">
+        <is>
+          <t>Sistema Integral de Asistencia y Monitoreo a la Conducción</t>
+        </is>
+      </c>
+      <c r="E130" s="14" t="n"/>
+      <c r="F130" s="15" t="n"/>
+    </row>
+    <row r="131" ht="30" customHeight="1">
+      <c r="A131" s="10" t="n"/>
+      <c r="B131" s="11" t="n"/>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D131" s="13" t="inlineStr">
+        <is>
+          <t>Integridad de componentes críticos del equipo (mecánicos, hidráulicos y eléctricos)</t>
+        </is>
+      </c>
+      <c r="E131" s="14" t="n"/>
+      <c r="F131" s="15" t="n"/>
+    </row>
+    <row r="132" ht="30" customHeight="1">
+      <c r="A132" s="10" t="n"/>
+      <c r="B132" s="11" t="n"/>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>CCP4</t>
+        </is>
+      </c>
+      <c r="D132" s="13" t="inlineStr">
+        <is>
+          <t>Infraestructura vial conforme a diseño (bermas, pretiles, radios, drenaje)</t>
+        </is>
+      </c>
+      <c r="E132" s="14" t="n"/>
+      <c r="F132" s="15" t="n"/>
+    </row>
+    <row r="133" ht="30" customHeight="1">
+      <c r="A133" s="10" t="n"/>
+      <c r="B133" s="11" t="n"/>
+      <c r="C133" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D133" s="17" t="inlineStr">
+        <is>
+          <t>Cabinas de protección (ROPS y FOPS)</t>
+        </is>
+      </c>
+      <c r="E133" s="14" t="n"/>
+      <c r="F133" s="15" t="n"/>
+    </row>
+    <row r="134" ht="30" customHeight="1">
+      <c r="A134" s="18" t="n"/>
+      <c r="B134" s="19" t="n"/>
+      <c r="C134" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D134" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta ante emergencia</t>
+        </is>
+      </c>
+      <c r="E134" s="22" t="n"/>
+      <c r="F134" s="23" t="n"/>
+    </row>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>RF 26: Equipos Autónomos</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Sistemas ODS y GPS (Navegación segura del equipo autónomo)
-CCP2 - Frenos, dirección, neumáticos y sistemas tecnológicos en condición segura
-CCP3 - Personal acreditado para operar y supervisar equipos autónomos
-CCP4 - Infraestructura vial para equipos autónomos (Rutas, Tránsito y Control de Acceso)
-CCM1 - Capacidad de respuesta ante emergencia y Parada de Emergencia</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="8" t="n"/>
-    </row>
-    <row r="31" ht="77.5" customHeight="1">
-      <c r="A31" s="4" t="n">
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Sistemas ODS y GPS (Navegación segura del equipo autónomo)</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="n"/>
+      <c r="F135" s="9" t="n"/>
+    </row>
+    <row r="136" ht="30" customHeight="1">
+      <c r="A136" s="10" t="n"/>
+      <c r="B136" s="11" t="n"/>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D136" s="13" t="inlineStr">
+        <is>
+          <t>Frenos, dirección, neumáticos y sistemas tecnológicos en condición segura</t>
+        </is>
+      </c>
+      <c r="E136" s="14" t="n"/>
+      <c r="F136" s="15" t="n"/>
+    </row>
+    <row r="137" ht="30" customHeight="1">
+      <c r="A137" s="10" t="n"/>
+      <c r="B137" s="11" t="n"/>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D137" s="13" t="inlineStr">
+        <is>
+          <t>Personal acreditado para operar y supervisar equipos autónomos</t>
+        </is>
+      </c>
+      <c r="E137" s="14" t="n"/>
+      <c r="F137" s="15" t="n"/>
+    </row>
+    <row r="138" ht="30" customHeight="1">
+      <c r="A138" s="10" t="n"/>
+      <c r="B138" s="11" t="n"/>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>CCP4</t>
+        </is>
+      </c>
+      <c r="D138" s="13" t="inlineStr">
+        <is>
+          <t>Infraestructura vial para equipos autónomos (Rutas, Tránsito y Control de Acceso)</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="n"/>
+      <c r="F138" s="15" t="n"/>
+    </row>
+    <row r="139" ht="30" customHeight="1">
+      <c r="A139" s="18" t="n"/>
+      <c r="B139" s="19" t="n"/>
+      <c r="C139" s="20" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D139" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta ante emergencia y Parada de Emergencia</t>
+        </is>
+      </c>
+      <c r="E139" s="22" t="n"/>
+      <c r="F139" s="23" t="n"/>
+    </row>
+    <row r="140" ht="30" customHeight="1">
+      <c r="A140" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B140" s="5" t="inlineStr">
         <is>
           <t>RF 27: Atropello</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Rutas Vehiculares y Peatonales conforme a diseño (segregación, señalética, iluminación)
-CCP2 - Sistema anti atropello y advertencia de proximidad
-CCP3 - Alta visibilidad en personas, vehículos y equipos
-CCP4 - Comunicación bidireccional efectiva entre personal y conductores
-CCM1 - Capacidad de respuesta ante emergencia</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="8" t="n"/>
-    </row>
-    <row r="32" ht="77.5" customHeight="1">
-      <c r="A32" s="4" t="n">
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>Rutas Vehiculares y Peatonales conforme a diseño (segregación, señalética, iluminación)</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="n"/>
+      <c r="F140" s="9" t="n"/>
+    </row>
+    <row r="141" ht="30" customHeight="1">
+      <c r="A141" s="10" t="n"/>
+      <c r="B141" s="11" t="n"/>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D141" s="13" t="inlineStr">
+        <is>
+          <t>Sistema anti atropello y advertencia de proximidad</t>
+        </is>
+      </c>
+      <c r="E141" s="14" t="n"/>
+      <c r="F141" s="15" t="n"/>
+    </row>
+    <row r="142" ht="30" customHeight="1">
+      <c r="A142" s="10" t="n"/>
+      <c r="B142" s="11" t="n"/>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D142" s="13" t="inlineStr">
+        <is>
+          <t>Alta visibilidad en personas, vehículos y equipos</t>
+        </is>
+      </c>
+      <c r="E142" s="14" t="n"/>
+      <c r="F142" s="15" t="n"/>
+    </row>
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="10" t="n"/>
+      <c r="B143" s="11" t="n"/>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>CCP4</t>
+        </is>
+      </c>
+      <c r="D143" s="13" t="inlineStr">
+        <is>
+          <t>Comunicación bidireccional efectiva entre personal y conductores</t>
+        </is>
+      </c>
+      <c r="E143" s="14" t="n"/>
+      <c r="F143" s="15" t="n"/>
+    </row>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="18" t="n"/>
+      <c r="B144" s="19" t="n"/>
+      <c r="C144" s="20" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D144" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta ante emergencia</t>
+        </is>
+      </c>
+      <c r="E144" s="22" t="n"/>
+      <c r="F144" s="23" t="n"/>
+    </row>
+    <row r="145" ht="30" customHeight="1">
+      <c r="A145" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B145" s="5" t="inlineStr">
         <is>
           <t>RF 28: Caving</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Sistema de monitoreo geomecánico y control de la producción
-CCP2 - Fracturamiento del macizo e Incorporación de áreas
-CCP3 - Perforación y tronadura conforme a diseño geotécnico
-CCM1 - Segregación y Control de Acceso
-CCM2 - Capacidad de Respuesta ante Emergencia</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="8" t="n"/>
-    </row>
-    <row r="33" ht="62" customHeight="1">
-      <c r="A33" s="4" t="n">
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>Sistema de monitoreo geomecánico y control de la producción</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="n"/>
+      <c r="F145" s="9" t="n"/>
+    </row>
+    <row r="146" ht="30" customHeight="1">
+      <c r="A146" s="10" t="n"/>
+      <c r="B146" s="11" t="n"/>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D146" s="13" t="inlineStr">
+        <is>
+          <t>Fracturamiento del macizo e Incorporación de áreas</t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="n"/>
+      <c r="F146" s="15" t="n"/>
+    </row>
+    <row r="147" ht="30" customHeight="1">
+      <c r="A147" s="10" t="n"/>
+      <c r="B147" s="11" t="n"/>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D147" s="13" t="inlineStr">
+        <is>
+          <t>Perforación y tronadura conforme a diseño geotécnico</t>
+        </is>
+      </c>
+      <c r="E147" s="14" t="n"/>
+      <c r="F147" s="15" t="n"/>
+    </row>
+    <row r="148" ht="30" customHeight="1">
+      <c r="A148" s="10" t="n"/>
+      <c r="B148" s="11" t="n"/>
+      <c r="C148" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D148" s="17" t="inlineStr">
+        <is>
+          <t>Segregación y Control de Acceso</t>
+        </is>
+      </c>
+      <c r="E148" s="14" t="n"/>
+      <c r="F148" s="15" t="n"/>
+    </row>
+    <row r="149" ht="30" customHeight="1">
+      <c r="A149" s="18" t="n"/>
+      <c r="B149" s="19" t="n"/>
+      <c r="C149" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D149" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de Respuesta ante Emergencia</t>
+        </is>
+      </c>
+      <c r="E149" s="22" t="n"/>
+      <c r="F149" s="23" t="n"/>
+    </row>
+    <row r="150" ht="30" customHeight="1">
+      <c r="A150" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>RF 29: Caída a Cuerpos Líquidos</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Zonas de cuerpos líquidos aisladas y señalizadas
-CCP2 - Personal capacitado para trabajos en cuerpos líquidos
-CCP3 - Infraestructura segura y comunicación operativa en cuerpos líquidos
-CCM1 - Capacidad de respuesta y rescate ante emergencia en cuerpos líquidos</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="8" t="n"/>
-    </row>
-    <row r="34" ht="77.5" customHeight="1">
-      <c r="A34" s="4" t="n">
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>Zonas de cuerpos líquidos aisladas y señalizadas</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="n"/>
+      <c r="F150" s="9" t="n"/>
+    </row>
+    <row r="151" ht="30" customHeight="1">
+      <c r="A151" s="10" t="n"/>
+      <c r="B151" s="11" t="n"/>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D151" s="13" t="inlineStr">
+        <is>
+          <t>Personal capacitado para trabajos en cuerpos líquidos</t>
+        </is>
+      </c>
+      <c r="E151" s="14" t="n"/>
+      <c r="F151" s="15" t="n"/>
+    </row>
+    <row r="152" ht="30" customHeight="1">
+      <c r="A152" s="10" t="n"/>
+      <c r="B152" s="11" t="n"/>
+      <c r="C152" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D152" s="13" t="inlineStr">
+        <is>
+          <t>Infraestructura segura y comunicación operativa en cuerpos líquidos</t>
+        </is>
+      </c>
+      <c r="E152" s="14" t="n"/>
+      <c r="F152" s="15" t="n"/>
+    </row>
+    <row r="153" ht="30" customHeight="1">
+      <c r="A153" s="18" t="n"/>
+      <c r="B153" s="19" t="n"/>
+      <c r="C153" s="20" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D153" s="21" t="inlineStr">
+        <is>
+          <t>Capacidad de respuesta y rescate ante emergencia en cuerpos líquidos</t>
+        </is>
+      </c>
+      <c r="E153" s="22" t="n"/>
+      <c r="F153" s="23" t="n"/>
+    </row>
+    <row r="154" ht="30" customHeight="1">
+      <c r="A154" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B154" s="5" t="inlineStr">
         <is>
           <t>RF 30: Tiro y Arrastre</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Sistemas de tiro y arrastre íntegros y operativos antes de uso
-CCP2 - Dispositivos de seguridad instalados y operativos en maniobras de arrastre
-CCP3 - Accesorios de arrastre certificados y áreas de maniobra señalizadas
-CCM1 - Barreras físicas instaladas para contener fallas de arrastre
-CCM2 - Respuesta inmediata ante emergencias en maniobras de arrastre</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="62" customHeight="1">
-      <c r="A35" s="4" t="n">
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>Sistemas de tiro y arrastre íntegros y operativos antes de uso</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="n"/>
+      <c r="F154" s="9" t="n"/>
+    </row>
+    <row r="155" ht="30" customHeight="1">
+      <c r="A155" s="10" t="n"/>
+      <c r="B155" s="11" t="n"/>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D155" s="13" t="inlineStr">
+        <is>
+          <t>Dispositivos de seguridad instalados y operativos en maniobras de arrastre</t>
+        </is>
+      </c>
+      <c r="E155" s="14" t="n"/>
+      <c r="F155" s="15" t="n"/>
+    </row>
+    <row r="156" ht="30" customHeight="1">
+      <c r="A156" s="10" t="n"/>
+      <c r="B156" s="11" t="n"/>
+      <c r="C156" s="12" t="inlineStr">
+        <is>
+          <t>CCP3</t>
+        </is>
+      </c>
+      <c r="D156" s="13" t="inlineStr">
+        <is>
+          <t>Accesorios de arrastre certificados y áreas de maniobra señalizadas</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="n"/>
+      <c r="F156" s="15" t="n"/>
+    </row>
+    <row r="157" ht="30" customHeight="1">
+      <c r="A157" s="10" t="n"/>
+      <c r="B157" s="11" t="n"/>
+      <c r="C157" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D157" s="17" t="inlineStr">
+        <is>
+          <t>Barreras físicas instaladas para contener fallas de arrastre</t>
+        </is>
+      </c>
+      <c r="E157" s="14" t="n"/>
+      <c r="F157" s="15" t="n"/>
+    </row>
+    <row r="158" ht="30" customHeight="1">
+      <c r="A158" s="18" t="n"/>
+      <c r="B158" s="19" t="n"/>
+      <c r="C158" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D158" s="21" t="inlineStr">
+        <is>
+          <t>Respuesta inmediata ante emergencias en maniobras de arrastre</t>
+        </is>
+      </c>
+      <c r="E158" s="22" t="n"/>
+      <c r="F158" s="23" t="n"/>
+    </row>
+    <row r="159" ht="30" customHeight="1">
+      <c r="A159" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B159" s="5" t="inlineStr">
         <is>
           <t>RF 31: Incendio de Equipos Mineros e Industriales</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>CCP1 - Operador acreditado y apto física/psicológicamente
-CCP2 - Integridad de sistemas eléctricos, hidráulicos, combustible y lubricación
-CCM1 - Sistema de detección y supresión de incendios
-CCM2 - Respuesta inmediata ante incendio en equipo</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Celdas en amarillo (columnas Implementación y Valorización CLP): a completar por el usuario.</t>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>CCP1</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>Operador acreditado y apto física/psicológicamente</t>
+        </is>
+      </c>
+      <c r="E159" s="8" t="n"/>
+      <c r="F159" s="9" t="n"/>
+    </row>
+    <row r="160" ht="30" customHeight="1">
+      <c r="A160" s="10" t="n"/>
+      <c r="B160" s="11" t="n"/>
+      <c r="C160" s="12" t="inlineStr">
+        <is>
+          <t>CCP2</t>
+        </is>
+      </c>
+      <c r="D160" s="13" t="inlineStr">
+        <is>
+          <t>Integridad de sistemas eléctricos, hidráulicos, combustible y lubricación</t>
+        </is>
+      </c>
+      <c r="E160" s="14" t="n"/>
+      <c r="F160" s="15" t="n"/>
+    </row>
+    <row r="161" ht="30" customHeight="1">
+      <c r="A161" s="10" t="n"/>
+      <c r="B161" s="11" t="n"/>
+      <c r="C161" s="16" t="inlineStr">
+        <is>
+          <t>CCM1</t>
+        </is>
+      </c>
+      <c r="D161" s="17" t="inlineStr">
+        <is>
+          <t>Sistema de detección y supresión de incendios</t>
+        </is>
+      </c>
+      <c r="E161" s="14" t="n"/>
+      <c r="F161" s="15" t="n"/>
+    </row>
+    <row r="162" ht="30" customHeight="1">
+      <c r="A162" s="18" t="n"/>
+      <c r="B162" s="19" t="n"/>
+      <c r="C162" s="20" t="inlineStr">
+        <is>
+          <t>CCM2</t>
+        </is>
+      </c>
+      <c r="D162" s="21" t="inlineStr">
+        <is>
+          <t>Respuesta inmediata ante incendio en equipo</t>
+        </is>
+      </c>
+      <c r="E162" s="22" t="n"/>
+      <c r="F162" s="23" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="26" t="inlineStr">
+        <is>
+          <t>Verde = CCP (Control Crítico Preventivo)   |   Naranjo = CCM (Control Crítico Mitigador)   |   Amarillo = celda a completar por el usuario (Implementación / Valorización CLP).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A37:E37"/>
+  <mergeCells count="65">
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="B97:B102"/>
+    <mergeCell ref="A154:A158"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="A113:A117"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="A164:F164"/>
+    <mergeCell ref="A69:A72"/>
+    <mergeCell ref="B108:B112"/>
+    <mergeCell ref="B124:B128"/>
+    <mergeCell ref="A5:A11"/>
+    <mergeCell ref="A84:A87"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B5:B11"/>
+    <mergeCell ref="A135:A139"/>
+    <mergeCell ref="B92:B96"/>
+    <mergeCell ref="A140:A144"/>
+    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="B73:B76"/>
+    <mergeCell ref="B88:B91"/>
+    <mergeCell ref="B113:B117"/>
+    <mergeCell ref="A77:A83"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="B154:B158"/>
+    <mergeCell ref="B63:B68"/>
+    <mergeCell ref="A118:A123"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B84:B87"/>
+    <mergeCell ref="B135:B139"/>
+    <mergeCell ref="A92:A96"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="B44:B49"/>
+    <mergeCell ref="B69:B72"/>
+    <mergeCell ref="A159:A162"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="A129:A134"/>
+    <mergeCell ref="B140:B144"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="B118:B123"/>
+    <mergeCell ref="A150:A153"/>
+    <mergeCell ref="A97:A102"/>
+    <mergeCell ref="A124:A128"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="B77:B83"/>
+    <mergeCell ref="A145:A149"/>
+    <mergeCell ref="A63:A68"/>
+    <mergeCell ref="B145:B149"/>
+    <mergeCell ref="B129:B134"/>
+    <mergeCell ref="A108:A112"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="A44:A49"/>
+    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="B159:B162"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
